--- a/data/trans_orig/IP3106-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3106-Clase-trans_orig.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19231</t>
+          <t>18815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35279</t>
+          <t>34845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71023</t>
+          <t>70797</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83641</t>
+          <t>83797</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66166</t>
+          <t>66369</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78389</t>
+          <t>78628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>140462</t>
+          <t>142795</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>159126</t>
+          <t>159594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18341</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>23534</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23307</t>
+          <t>23385</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39633</t>
+          <t>39461</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53043</t>
+          <t>52173</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65341</t>
+          <t>64835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55350</t>
+          <t>55947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67899</t>
+          <t>68561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112724</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130584</t>
+          <t>130087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>19228</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28481</t>
+          <t>28183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26217</t>
+          <t>26483</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42863</t>
+          <t>43481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39921</t>
+          <t>39975</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51232</t>
+          <t>51067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
+          <t>63461</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76918</t>
+          <t>76392</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>107451</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125559</t>
+          <t>125147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27990</t>
+          <t>28340</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44784</t>
+          <t>44816</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>26888</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44507</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>59839</t>
+          <t>59506</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84063</t>
+          <t>83931</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>139489</t>
+          <t>140850</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>157928</t>
+          <t>157940</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>133404</t>
+          <t>132100</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151711</t>
+          <t>151148</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>278016</t>
+          <t>278760</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>304735</t>
+          <t>305203</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28495</t>
+          <t>28777</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>20659</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>21793</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>37867</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>65291</t>
+          <t>65152</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>79589</t>
+          <t>79406</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>84108</t>
+          <t>84454</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>98574</t>
+          <t>98645</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>153869</t>
+          <t>154998</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>174053</t>
+          <t>175045</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15458</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5160,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11712</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>22386</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>11949</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>24262</t>
+          <t>24354</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>26468</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>43040</t>
+          <t>42473</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>43591</t>
+          <t>43286</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>55717</t>
+          <t>55846</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>36311</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>49367</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>84108</t>
+          <t>83579</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>100621</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,7%</t>
         </is>
       </c>
     </row>
@@ -5651,12 +5651,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -5842,12 +5842,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>22618</t>
+          <t>23571</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>40362</t>
+          <t>41358</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5857,12 +5857,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>24766</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>43112</t>
+          <t>42995</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>52615</t>
+          <t>53093</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>77059</t>
+          <t>77049</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>93844</t>
+          <t>92691</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>124425</t>
+          <t>124081</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>104392</t>
+          <t>102814</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>135141</t>
+          <t>135258</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>205372</t>
+          <t>205794</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>249203</t>
+          <t>252924</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>438728</t>
+          <t>439466</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>472719</t>
+          <t>473438</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>466519</t>
+          <t>466007</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>501071</t>
+          <t>500807</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>916273</t>
+          <t>914291</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>965450</t>
+          <t>963283</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -6763,7 +6763,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6999,12 +6999,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7019,12 +7019,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -7097,12 +7097,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74470</t>
+          <t>74733</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82158</t>
+          <t>82314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7132,12 +7132,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66155</t>
+          <t>65658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75220</t>
+          <t>74948</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>142694</t>
+          <t>144300</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>155660</t>
+          <t>155469</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -7779,12 +7779,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>11810</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20176</t>
+          <t>19864</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73813</t>
+          <t>73304</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81782</t>
+          <t>81842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7907,12 +7907,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7927,12 +7927,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73929</t>
+          <t>74288</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84284</t>
+          <t>84277</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7962,12 +7962,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150262</t>
+          <t>150552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163709</t>
+          <t>163977</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -8574,12 +8574,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -8687,12 +8687,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67699</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76379</t>
+          <t>76235</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>67473</t>
+          <t>67855</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76563</t>
+          <t>76608</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>139316</t>
+          <t>138934</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>151160</t>
+          <t>151077</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -9256,12 +9256,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -9369,12 +9369,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>18928</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29136</t>
+          <t>28498</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9454,12 +9454,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -9482,12 +9482,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>163651</t>
+          <t>164358</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>176188</t>
+          <t>176353</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>177694</t>
+          <t>177824</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>192678</t>
+          <t>192479</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9532,12 +9532,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>346209</t>
+          <t>346963</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>365388</t>
+          <t>365306</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -10051,12 +10051,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11091</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10121,12 +10121,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10136,12 +10136,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -10164,12 +10164,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14292</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>28631</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -10277,12 +10277,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>114134</t>
+          <t>114047</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>126339</t>
+          <t>126453</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>109552</t>
+          <t>108946</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>120865</t>
+          <t>120950</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10347,12 +10347,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>226957</t>
+          <t>227421</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>245194</t>
+          <t>245335</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -10959,12 +10959,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10994,12 +10994,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11029,12 +11029,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>10804</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -11072,12 +11072,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>42845</t>
+          <t>43185</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>48564</t>
+          <t>48617</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11087,12 +11087,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>58804</t>
+          <t>58663</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>65902</t>
+          <t>65611</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>104129</t>
+          <t>104815</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>112863</t>
+          <t>113361</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11533,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11563,12 +11563,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -11641,12 +11641,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>24099</t>
+          <t>23127</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11711,12 +11711,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>41749</t>
+          <t>41633</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -11754,12 +11754,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>25854</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>45630</t>
+          <t>44999</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>36773</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>58929</t>
+          <t>57658</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>67248</t>
+          <t>68315</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>97151</t>
+          <t>97916</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -11867,12 +11867,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>557360</t>
+          <t>557733</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>580871</t>
+          <t>580004</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -11882,12 +11882,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -11902,12 +11902,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>574297</t>
+          <t>577768</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>600782</t>
+          <t>601960</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -11937,12 +11937,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1137766</t>
+          <t>1140787</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1175026</t>
+          <t>1174305</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12705,12 +12705,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12740,12 +12740,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12755,12 +12755,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -12783,12 +12783,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12798,12 +12798,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12818,12 +12818,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12833,12 +12833,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12868,12 +12868,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -12896,12 +12896,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57840</t>
+          <t>57571</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68029</t>
+          <t>67784</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12931,12 +12931,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72627</t>
+          <t>73853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83203</t>
+          <t>83883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12946,12 +12946,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>135927</t>
+          <t>135446</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>149838</t>
+          <t>148762</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12981,12 +12981,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13500,12 +13500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -13578,12 +13578,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15698</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13593,12 +13593,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -13613,12 +13613,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -13648,12 +13648,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>27634</t>
+          <t>27618</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -13691,12 +13691,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77504</t>
+          <t>77765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87462</t>
+          <t>88207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13706,12 +13706,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13726,12 +13726,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85305</t>
+          <t>85005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96382</t>
+          <t>96470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13761,12 +13761,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166651</t>
+          <t>166776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>182115</t>
+          <t>181427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -14265,7 +14265,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14330,12 +14330,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -14373,12 +14373,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14388,12 +14388,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14408,12 +14408,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14443,12 +14443,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9809</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21544</t>
+          <t>21702</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -14486,12 +14486,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43233</t>
+          <t>43247</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51991</t>
+          <t>51921</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14501,12 +14501,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -14521,12 +14521,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55265</t>
+          <t>55174</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>64775</t>
+          <t>64809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14536,12 +14536,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>101126</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>114564</t>
+          <t>114311</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -14947,7 +14947,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -15055,12 +15055,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9803</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15070,12 +15070,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15090,12 +15090,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15125,12 +15125,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24483</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15183,12 +15183,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>28040</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15238,12 +15238,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>27691</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46215</t>
+          <t>46409</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15253,12 +15253,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -15281,12 +15281,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>176253</t>
+          <t>175677</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>190829</t>
+          <t>190498</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15296,12 +15296,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>166231</t>
+          <t>165913</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>181828</t>
+          <t>181835</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -15351,12 +15351,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>346978</t>
+          <t>347639</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>369739</t>
+          <t>368510</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -15850,12 +15850,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15900,12 +15900,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15920,12 +15920,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13963</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -15963,12 +15963,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>22653</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15978,12 +15978,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15998,12 +15998,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>34410</t>
+          <t>33771</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -16076,12 +16076,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>102368</t>
+          <t>101913</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>116311</t>
+          <t>116163</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -16091,12 +16091,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -16111,12 +16111,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>112379</t>
+          <t>111917</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>125198</t>
+          <t>124631</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>219598</t>
+          <t>219144</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>237862</t>
+          <t>238220</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -16572,7 +16572,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -16645,12 +16645,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -16660,12 +16660,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -16715,12 +16715,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -16758,12 +16758,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -16773,12 +16773,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -16793,12 +16793,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>16749</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -16808,12 +16808,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -16828,12 +16828,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>24998</t>
+          <t>25546</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -16843,12 +16843,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -16871,12 +16871,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>40562</t>
+          <t>41663</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>50116</t>
+          <t>50753</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16886,12 +16886,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16906,12 +16906,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>47363</t>
+          <t>47170</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>57808</t>
+          <t>57942</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16921,12 +16921,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16941,12 +16941,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>92873</t>
+          <t>92936</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>106718</t>
+          <t>106652</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16956,12 +16956,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -17367,7 +17367,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>779</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -17440,12 +17440,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>24068</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -17475,12 +17475,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -17510,12 +17510,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>27922</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48395</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -17525,12 +17525,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -17553,12 +17553,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>56468</t>
+          <t>56029</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>82144</t>
+          <t>81539</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -17568,12 +17568,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -17588,12 +17588,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>51359</t>
+          <t>51182</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>77328</t>
+          <t>77995</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -17603,12 +17603,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -17623,12 +17623,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>113306</t>
+          <t>114150</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>149818</t>
+          <t>149426</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -17638,12 +17638,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -17666,12 +17666,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>519515</t>
+          <t>520437</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>548566</t>
+          <t>548478</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -17681,82 +17681,82 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
+          <t>88,29%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>579363</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>565346</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>593364</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>87,14%</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>85,03%</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>1115419</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>1095720</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>1135688</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>86,73%</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>85,2%</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
           <t>88,31%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>579363</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>563862</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>592661</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>87,14%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>84,8%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>89,14%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>1115419</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>1096077</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>1135956</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>86,73%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>85,23%</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -18446,7 +18446,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -18469,12 +18469,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -18484,12 +18484,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -18504,12 +18504,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -18519,12 +18519,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -18539,12 +18539,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -18554,12 +18554,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -18582,12 +18582,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26038</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -18597,12 +18597,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -18617,12 +18617,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>27116</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -18632,12 +18632,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -18652,12 +18652,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28334</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47049</t>
+          <t>47765</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -18667,12 +18667,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -18695,12 +18695,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69436</t>
+          <t>69824</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83899</t>
+          <t>83506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -18710,12 +18710,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -18730,12 +18730,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102224</t>
+          <t>102139</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117613</t>
+          <t>118039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -18745,12 +18745,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -18765,12 +18765,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>176155</t>
+          <t>176118</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>198365</t>
+          <t>198094</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -18780,12 +18780,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -19015,7 +19015,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -19264,12 +19264,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -19279,12 +19279,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -19304,7 +19304,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -19334,12 +19334,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -19377,12 +19377,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34036</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -19412,12 +19412,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>17809</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32739</t>
+          <t>32191</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -19427,12 +19427,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -19447,12 +19447,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40279</t>
+          <t>39708</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>60605</t>
+          <t>60304</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -19462,12 +19462,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -19490,12 +19490,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56382</t>
+          <t>57494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71818</t>
+          <t>71970</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -19505,12 +19505,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -19525,12 +19525,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57760</t>
+          <t>58253</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>73434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -19540,12 +19540,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -19560,12 +19560,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119842</t>
+          <t>120962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141343</t>
+          <t>141898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -19575,12 +19575,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -20064,7 +20064,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -20079,7 +20079,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -20094,12 +20094,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>9947</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -20109,12 +20109,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -20129,12 +20129,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -20144,12 +20144,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -20172,12 +20172,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17291</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -20187,12 +20187,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -20207,12 +20207,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>18762</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -20222,12 +20222,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -20242,12 +20242,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32531</t>
+          <t>32804</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -20257,12 +20257,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -20285,12 +20285,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32236</t>
+          <t>32341</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42986</t>
+          <t>42787</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -20300,12 +20300,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -20320,12 +20320,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36555</t>
+          <t>37377</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49425</t>
+          <t>50285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -20335,12 +20335,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -20355,12 +20355,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>73239</t>
+          <t>72947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89382</t>
+          <t>89346</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -20370,12 +20370,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -20746,7 +20746,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -20776,12 +20776,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -20791,12 +20791,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -20811,12 +20811,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -20854,12 +20854,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -20869,12 +20869,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -20889,12 +20889,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21045</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -20904,12 +20904,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -20924,12 +20924,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14590</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30521</t>
+          <t>31880</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -20939,12 +20939,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -20967,12 +20967,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44667</t>
+          <t>44929</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>123809</t>
+          <t>115752</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -21002,12 +21002,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>72141</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -21017,12 +21017,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -21037,12 +21037,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>96367</t>
+          <t>97261</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>182646</t>
+          <t>195587</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -21052,12 +21052,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -21080,12 +21080,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>86923</t>
+          <t>91517</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>160590</t>
+          <t>160627</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -21095,12 +21095,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -21115,12 +21115,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>126016</t>
+          <t>125365</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>155334</t>
+          <t>155842</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -21130,12 +21130,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -21150,12 +21150,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>223936</t>
+          <t>214505</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>304765</t>
+          <t>304165</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -21165,12 +21165,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -21536,12 +21536,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -21591,7 +21591,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -21606,12 +21606,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>889</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -21621,12 +21621,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -21649,12 +21649,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -21664,12 +21664,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -21684,12 +21684,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26377</t>
+          <t>25830</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -21699,12 +21699,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -21719,12 +21719,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>18672</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>35203</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -21734,12 +21734,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -21762,12 +21762,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>36412</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -21777,12 +21777,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -21797,12 +21797,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>42343</t>
+          <t>41389</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -21812,12 +21812,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -21832,12 +21832,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>43925</t>
+          <t>43305</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>70517</t>
+          <t>68807</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -21847,12 +21847,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -21875,12 +21875,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>69072</t>
+          <t>70321</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>88159</t>
+          <t>88497</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -21890,12 +21890,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -21910,12 +21910,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>96804</t>
+          <t>96933</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>122451</t>
+          <t>122241</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -21925,12 +21925,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -21945,12 +21945,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>173987</t>
+          <t>173929</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>205479</t>
+          <t>203374</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -21960,12 +21960,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,11%</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>366</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -22346,12 +22346,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -22401,12 +22401,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>373</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -22421,7 +22421,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -22459,12 +22459,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -22479,12 +22479,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>18331</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -22494,12 +22494,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -22514,12 +22514,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>23359</t>
+          <t>23375</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -22557,12 +22557,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -22572,12 +22572,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -22592,12 +22592,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>30135</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -22607,12 +22607,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -22627,12 +22627,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>28599</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>46159</t>
+          <t>46526</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -22642,12 +22642,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -22670,12 +22670,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>42932</t>
+          <t>43707</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>55487</t>
+          <t>55340</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -22685,12 +22685,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -22705,12 +22705,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>26346</t>
+          <t>27004</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>41758</t>
+          <t>42595</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -22720,12 +22720,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -22740,12 +22740,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>73629</t>
+          <t>73570</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>93671</t>
+          <t>93728</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -22755,12 +22755,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -22940,7 +22940,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -22955,7 +22955,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -22990,7 +22990,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -23126,12 +23126,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -23141,12 +23141,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -23161,12 +23161,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -23176,12 +23176,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -23196,12 +23196,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>17698</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -23239,12 +23239,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>22883</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -23254,12 +23254,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>43853</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>71039</t>
+          <t>71113</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -23289,12 +23289,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -23309,12 +23309,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>69353</t>
+          <t>71239</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>102074</t>
+          <t>102445</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -23324,12 +23324,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>136238</t>
+          <t>135288</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>231737</t>
+          <t>234935</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -23367,12 +23367,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -23387,12 +23387,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>143836</t>
+          <t>141809</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>189902</t>
+          <t>188629</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -23402,12 +23402,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -23422,12 +23422,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>293977</t>
+          <t>290512</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>407607</t>
+          <t>401527</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -23437,12 +23437,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -23465,12 +23465,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>381780</t>
+          <t>388002</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>473228</t>
+          <t>474089</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -23480,12 +23480,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -23500,12 +23500,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>478165</t>
+          <t>479848</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>530544</t>
+          <t>530875</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -23515,12 +23515,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -23535,12 +23535,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>881423</t>
+          <t>885398</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>989722</t>
+          <t>989642</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -23550,12 +23550,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
